--- a/corpus/C02.xlsx
+++ b/corpus/C02.xlsx
@@ -753,75 +753,75 @@
       </c>
       <c r="I5">
         <f>H9</f>
-        <v>7718.0</v>
+        <v>7470.0</v>
       </c>
       <c r="J5">
         <f>I9</f>
-        <v>7983.0</v>
+        <v>7727.0</v>
       </c>
       <c r="K5">
         <f>J9</f>
-        <v>8257.0</v>
+        <v>7993.0</v>
       </c>
       <c r="L5">
         <f>K9</f>
-        <v>8541.0</v>
+        <v>8268.0</v>
       </c>
       <c r="M5">
         <f>L9</f>
-        <v>8835.0</v>
+        <v>8553.0</v>
       </c>
       <c r="N5">
         <f>M9</f>
-        <v>9139.0</v>
+        <v>8847.0</v>
       </c>
       <c r="O5">
         <f>N9</f>
-        <v>9453.0</v>
+        <v>9151.0</v>
       </c>
       <c r="P5">
         <f>O9</f>
-        <v>9778.0</v>
+        <v>9466.0</v>
       </c>
       <c r="Q5">
         <f>P9</f>
-        <v>10114.0</v>
+        <v>9791.0</v>
       </c>
       <c r="R5">
         <f>Q9</f>
-        <v>10462.0</v>
+        <v>10128.0</v>
       </c>
       <c r="S5">
         <f>R9</f>
-        <v>10822.0</v>
+        <v>10476.0</v>
       </c>
       <c r="T5">
         <f>S9</f>
-        <v>11195.0</v>
+        <v>10837.0</v>
       </c>
       <c r="U5">
         <f>T9</f>
-        <v>11580.0</v>
+        <v>11209.0</v>
       </c>
       <c r="V5">
         <f>U9</f>
-        <v>11978.0</v>
+        <v>11595.0</v>
       </c>
       <c r="W5">
         <f>V9</f>
-        <v>12390.0</v>
+        <v>11994.0</v>
       </c>
       <c r="X5">
         <f>W9</f>
-        <v>12816.0</v>
+        <v>12406.0</v>
       </c>
       <c r="Y5">
         <f>X9</f>
-        <v>13257.0</v>
+        <v>12833.0</v>
       </c>
       <c r="Z5">
         <f>Y9</f>
-        <v>13713.0</v>
+        <v>13275.0</v>
       </c>
     </row>
     <row r="6">
@@ -856,75 +856,75 @@
       </c>
       <c r="I6">
         <f>ROUND(I5*Assumptions!$B$5,0)</f>
-        <v>446.0</v>
+        <v>432.0</v>
       </c>
       <c r="J6">
         <f>ROUND(J5*Assumptions!$B$5,0)</f>
-        <v>461.0</v>
+        <v>447.0</v>
       </c>
       <c r="K6">
         <f>ROUND(K5*Assumptions!$B$5,0)</f>
-        <v>477.0</v>
+        <v>462.0</v>
       </c>
       <c r="L6">
         <f>ROUND(L5*Assumptions!$B$5,0)</f>
-        <v>494.0</v>
+        <v>478.0</v>
       </c>
       <c r="M6">
         <f>ROUND(M5*Assumptions!$B$5,0)</f>
-        <v>511.0</v>
+        <v>494.0</v>
       </c>
       <c r="N6">
         <f>ROUND(N5*Assumptions!$B$5,0)</f>
-        <v>528.0</v>
+        <v>511.0</v>
       </c>
       <c r="O6">
         <f>ROUND(O5*Assumptions!$B$5,0)</f>
-        <v>546.0</v>
+        <v>529.0</v>
       </c>
       <c r="P6">
         <f>ROUND(P5*Assumptions!$B$5,0)</f>
-        <v>565.0</v>
+        <v>547.0</v>
       </c>
       <c r="Q6">
         <f>ROUND(Q5*Assumptions!$B$5,0)</f>
-        <v>585.0</v>
+        <v>566.0</v>
       </c>
       <c r="R6">
         <f>ROUND(R5*Assumptions!$B$5,0)</f>
-        <v>605.0</v>
+        <v>585.0</v>
       </c>
       <c r="S6">
         <f>ROUND(S5*Assumptions!$B$5,0)</f>
-        <v>626.0</v>
+        <v>606.0</v>
       </c>
       <c r="T6">
         <f>ROUND(T5*Assumptions!$B$5,0)</f>
-        <v>647.0</v>
+        <v>626.0</v>
       </c>
       <c r="U6">
         <f>ROUND(U5*Assumptions!$B$5,0)</f>
-        <v>669.0</v>
+        <v>648.0</v>
       </c>
       <c r="V6">
         <f>ROUND(V5*Assumptions!$B$5,0)</f>
-        <v>692.0</v>
+        <v>670.0</v>
       </c>
       <c r="W6">
         <f>ROUND(W5*Assumptions!$B$5,0)</f>
-        <v>716.0</v>
+        <v>693.0</v>
       </c>
       <c r="X6">
         <f>ROUND(X5*Assumptions!$B$5,0)</f>
-        <v>741.0</v>
+        <v>717.0</v>
       </c>
       <c r="Y6">
         <f>ROUND(Y5*Assumptions!$B$5,0)</f>
-        <v>766.0</v>
+        <v>742.0</v>
       </c>
       <c r="Z6">
         <f>ROUND(Z5*Assumptions!$B$5,0)</f>
-        <v>793.0</v>
+        <v>767.0</v>
       </c>
     </row>
     <row r="7">
@@ -959,75 +959,75 @@
       </c>
       <c r="I7">
         <f>-ROUND(I5*Assumptions!$B$6,0)</f>
-        <v>-181.0</v>
+        <v>-175.0</v>
       </c>
       <c r="J7">
         <f>-ROUND(J5*Assumptions!$B$6,0)</f>
-        <v>-187.0</v>
+        <v>-181.0</v>
       </c>
       <c r="K7">
         <f>-ROUND(K5*Assumptions!$B$6,0)</f>
-        <v>-193.0</v>
+        <v>-187.0</v>
       </c>
       <c r="L7">
         <f>-ROUND(L5*Assumptions!$B$6,0)</f>
-        <v>-200.0</v>
+        <v>-193.0</v>
       </c>
       <c r="M7">
         <f>-ROUND(M5*Assumptions!$B$6,0)</f>
-        <v>-207.0</v>
+        <v>-200.0</v>
       </c>
       <c r="N7">
         <f>-ROUND(N5*Assumptions!$B$6,0)</f>
-        <v>-214.0</v>
+        <v>-207.0</v>
       </c>
       <c r="O7">
         <f>-ROUND(O5*Assumptions!$B$6,0)</f>
-        <v>-221.0</v>
+        <v>-214.0</v>
       </c>
       <c r="P7">
         <f>-ROUND(P5*Assumptions!$B$6,0)</f>
-        <v>-229.0</v>
+        <v>-222.0</v>
       </c>
       <c r="Q7">
         <f>-ROUND(Q5*Assumptions!$B$6,0)</f>
-        <v>-237.0</v>
+        <v>-229.0</v>
       </c>
       <c r="R7">
         <f>-ROUND(R5*Assumptions!$B$6,0)</f>
-        <v>-245.0</v>
+        <v>-237.0</v>
       </c>
       <c r="S7">
         <f>-ROUND(S5*Assumptions!$B$6,0)</f>
-        <v>-253.0</v>
+        <v>-245.0</v>
       </c>
       <c r="T7">
         <f>-ROUND(T5*Assumptions!$B$6,0)</f>
-        <v>-262.0</v>
+        <v>-254.0</v>
       </c>
       <c r="U7">
         <f>-ROUND(U5*Assumptions!$B$6,0)</f>
-        <v>-271.0</v>
+        <v>-262.0</v>
       </c>
       <c r="V7">
         <f>-ROUND(V5*Assumptions!$B$6,0)</f>
-        <v>-280.0</v>
+        <v>-271.0</v>
       </c>
       <c r="W7">
         <f>-ROUND(W5*Assumptions!$B$6,0)</f>
-        <v>-290.0</v>
+        <v>-281.0</v>
       </c>
       <c r="X7">
         <f>-ROUND(X5*Assumptions!$B$6,0)</f>
-        <v>-300.0</v>
+        <v>-290.0</v>
       </c>
       <c r="Y7">
         <f>-ROUND(Y5*Assumptions!$B$6,0)</f>
-        <v>-310.0</v>
+        <v>-300.0</v>
       </c>
       <c r="Z7">
         <f>-ROUND(Z5*Assumptions!$B$6,0)</f>
-        <v>-321.0</v>
+        <v>-311.0</v>
       </c>
     </row>
     <row r="9">
@@ -1057,80 +1057,80 @@
         <v>7462.0</v>
       </c>
       <c r="H9">
-        <f>H5+H6+H7</f>
-        <v>7718.0</v>
+        <f>G5+H6+H7</f>
+        <v>7470.0</v>
       </c>
       <c r="I9">
         <f>I5+I6+I7</f>
-        <v>7983.0</v>
+        <v>7727.0</v>
       </c>
       <c r="J9">
         <f>J5+J6+J7</f>
-        <v>8257.0</v>
+        <v>7993.0</v>
       </c>
       <c r="K9">
         <f>K5+K6+K7</f>
-        <v>8541.0</v>
+        <v>8268.0</v>
       </c>
       <c r="L9">
         <f>L5+L6+L7</f>
-        <v>8835.0</v>
+        <v>8553.0</v>
       </c>
       <c r="M9">
         <f>M5+M6+M7</f>
-        <v>9139.0</v>
+        <v>8847.0</v>
       </c>
       <c r="N9">
         <f>N5+N6+N7</f>
-        <v>9453.0</v>
+        <v>9151.0</v>
       </c>
       <c r="O9">
         <f>O5+O6+O7</f>
-        <v>9778.0</v>
+        <v>9466.0</v>
       </c>
       <c r="P9">
         <f>P5+P6+P7</f>
-        <v>10114.0</v>
+        <v>9791.0</v>
       </c>
       <c r="Q9">
         <f>Q5+Q6+Q7</f>
-        <v>10462.0</v>
+        <v>10128.0</v>
       </c>
       <c r="R9">
         <f>R5+R6+R7</f>
-        <v>10822.0</v>
+        <v>10476.0</v>
       </c>
       <c r="S9">
         <f>S5+S6+S7</f>
-        <v>11195.0</v>
+        <v>10837.0</v>
       </c>
       <c r="T9">
         <f>T5+T6+T7</f>
-        <v>11580.0</v>
+        <v>11209.0</v>
       </c>
       <c r="U9">
         <f>U5+U6+U7</f>
-        <v>11978.0</v>
+        <v>11595.0</v>
       </c>
       <c r="V9">
         <f>V5+V6+V7</f>
-        <v>12390.0</v>
+        <v>11994.0</v>
       </c>
       <c r="W9">
         <f>W5+W6+W7</f>
-        <v>12816.0</v>
+        <v>12406.0</v>
       </c>
       <c r="X9">
         <f>X5+X6+X7</f>
-        <v>13257.0</v>
+        <v>12833.0</v>
       </c>
       <c r="Y9">
         <f>Y5+Y6+Y7</f>
-        <v>13713.0</v>
+        <v>13275.0</v>
       </c>
       <c r="Z9">
         <f>Z5+Z6+Z7</f>
-        <v>14185.0</v>
+        <v>13731.0</v>
       </c>
     </row>
     <row r="11">
@@ -1264,79 +1264,79 @@
       </c>
       <c r="H13">
         <f>ROUND((H5+H9)/2,0)</f>
-        <v>7590.0</v>
+        <v>7466.0</v>
       </c>
       <c r="I13">
         <f>ROUND((I5+I9)/2,0)</f>
-        <v>7851.0</v>
+        <v>7599.0</v>
       </c>
       <c r="J13">
         <f>ROUND((J5+J9)/2,0)</f>
-        <v>8120.0</v>
+        <v>7860.0</v>
       </c>
       <c r="K13">
         <f>ROUND((K5+K9)/2,0)</f>
-        <v>8399.0</v>
+        <v>8131.0</v>
       </c>
       <c r="L13">
         <f>ROUND((L5+L9)/2,0)</f>
-        <v>8688.0</v>
+        <v>8411.0</v>
       </c>
       <c r="M13">
         <f>ROUND((M5+M9)/2,0)</f>
-        <v>8987.0</v>
+        <v>8700.0</v>
       </c>
       <c r="N13">
         <f>ROUND((N5+N9)/2,0)</f>
-        <v>9296.0</v>
+        <v>8999.0</v>
       </c>
       <c r="O13">
         <f>ROUND((O5+O9)/2,0)</f>
-        <v>9616.0</v>
+        <v>9309.0</v>
       </c>
       <c r="P13">
         <f>ROUND((P5+P9)/2,0)</f>
-        <v>9946.0</v>
+        <v>9629.0</v>
       </c>
       <c r="Q13">
         <f>ROUND((Q5+Q9)/2,0)</f>
-        <v>10288.0</v>
+        <v>9960.0</v>
       </c>
       <c r="R13">
         <f>ROUND((R5+R9)/2,0)</f>
-        <v>10642.0</v>
+        <v>10302.0</v>
       </c>
       <c r="S13">
         <f>ROUND((S5+S9)/2,0)</f>
-        <v>11009.0</v>
+        <v>10657.0</v>
       </c>
       <c r="T13">
         <f>ROUND((T5+T9)/2,0)</f>
-        <v>11388.0</v>
+        <v>11023.0</v>
       </c>
       <c r="U13">
         <f>ROUND((U5+U9)/2,0)</f>
-        <v>11779.0</v>
+        <v>11402.0</v>
       </c>
       <c r="V13">
         <f>ROUND((V5+V9)/2,0)</f>
-        <v>12184.0</v>
+        <v>11795.0</v>
       </c>
       <c r="W13">
         <f>ROUND((W5+W9)/2,0)</f>
-        <v>12603.0</v>
+        <v>12200.0</v>
       </c>
       <c r="X13">
         <f>ROUND((X5+X9)/2,0)</f>
-        <v>13037.0</v>
+        <v>12620.0</v>
       </c>
       <c r="Y13">
         <f>ROUND((Y5+Y9)/2,0)</f>
-        <v>13485.0</v>
+        <v>13054.0</v>
       </c>
       <c r="Z13">
         <f>ROUND((Z5+Z9)/2,0)</f>
-        <v>13949.0</v>
+        <v>13503.0</v>
       </c>
     </row>
     <row r="15">
@@ -1367,79 +1367,79 @@
       </c>
       <c r="H15">
         <f>ROUND(H13*H11,0)</f>
-        <v>947460.0</v>
+        <v>931981.0</v>
       </c>
       <c r="I15">
         <f>ROUND(I13*I11,0)</f>
-        <v>989540.0</v>
+        <v>957778.0</v>
       </c>
       <c r="J15">
         <f>ROUND(J13*J11,0)</f>
-        <v>1033351.0</v>
+        <v>1000264.0</v>
       </c>
       <c r="K15">
         <f>ROUND(K13*K11,0)</f>
-        <v>1079188.0</v>
+        <v>1044752.0</v>
       </c>
       <c r="L15">
         <f>ROUND(L13*L11,0)</f>
-        <v>1127181.0</v>
+        <v>1091243.0</v>
       </c>
       <c r="M15">
         <f>ROUND(M13*M11,0)</f>
-        <v>1177297.0</v>
+        <v>1139700.0</v>
       </c>
       <c r="N15">
         <f>ROUND(N13*N11,0)</f>
-        <v>1229582.0</v>
+        <v>1190298.0</v>
       </c>
       <c r="O15">
         <f>ROUND(O13*O11,0)</f>
-        <v>1284217.0</v>
+        <v>1243217.0</v>
       </c>
       <c r="P15">
         <f>ROUND(P13*P11,0)</f>
-        <v>1341218.0</v>
+        <v>1298471.0</v>
       </c>
       <c r="Q15">
         <f>ROUND(Q13*Q11,0)</f>
-        <v>1400814.0</v>
+        <v>1356154.0</v>
       </c>
       <c r="R15">
         <f>ROUND(R13*R11,0)</f>
-        <v>1463062.0</v>
+        <v>1416319.0</v>
       </c>
       <c r="S15">
         <f>ROUND(S13*S11,0)</f>
-        <v>1528159.0</v>
+        <v>1479298.0</v>
       </c>
       <c r="T15">
         <f>ROUND(T13*T11,0)</f>
-        <v>1596142.0</v>
+        <v>1544984.0</v>
       </c>
       <c r="U15">
         <f>ROUND(U13*U11,0)</f>
-        <v>1666964.0</v>
+        <v>1613611.0</v>
       </c>
       <c r="V15">
         <f>ROUND(V13*V11,0)</f>
-        <v>1740972.0</v>
+        <v>1685388.0</v>
       </c>
       <c r="W15">
         <f>ROUND(W13*W11,0)</f>
-        <v>1818361.0</v>
+        <v>1760216.0</v>
       </c>
       <c r="X15">
         <f>ROUND(X13*X11,0)</f>
-        <v>1899230.0</v>
+        <v>1838482.0</v>
       </c>
       <c r="Y15">
         <f>ROUND(Y13*Y11,0)</f>
-        <v>1983509.0</v>
+        <v>1920113.0</v>
       </c>
       <c r="Z15">
         <f>ROUND(Z13*Z11,0)</f>
-        <v>2071705.0</v>
+        <v>2005466.0</v>
       </c>
     </row>
     <row r="17">
@@ -1470,79 +1470,79 @@
       </c>
       <c r="H17">
         <f>G17+H15</f>
-        <v>5113461.0</v>
+        <v>5097982.0</v>
       </c>
       <c r="I17">
         <f>H17+I15</f>
-        <v>6103001.0</v>
+        <v>6055760.0</v>
       </c>
       <c r="J17">
         <f>I17+J15</f>
-        <v>7136352.0</v>
+        <v>7056024.0</v>
       </c>
       <c r="K17">
         <f>J17+K15</f>
-        <v>8215540.0</v>
+        <v>8100776.0</v>
       </c>
       <c r="L17">
         <f>K17+L15</f>
-        <v>9342721.0</v>
+        <v>9192019.0</v>
       </c>
       <c r="M17">
         <f>L17+M15</f>
-        <v>10520018.0</v>
+        <v>10331719.0</v>
       </c>
       <c r="N17">
         <f>M17+N15</f>
-        <v>11749600.0</v>
+        <v>11522017.0</v>
       </c>
       <c r="O17">
         <f>N17+O15</f>
-        <v>13033817.0</v>
+        <v>12765234.0</v>
       </c>
       <c r="P17">
         <f>O17+P15</f>
-        <v>14375035.0</v>
+        <v>14063705.0</v>
       </c>
       <c r="Q17">
         <f>P17+Q15</f>
-        <v>15775849.0</v>
+        <v>15419859.0</v>
       </c>
       <c r="R17">
         <f>Q17+R15</f>
-        <v>17238911.0</v>
+        <v>16836178.0</v>
       </c>
       <c r="S17">
         <f>R17+S15</f>
-        <v>18767070.0</v>
+        <v>18315476.0</v>
       </c>
       <c r="T17">
         <f>S17+T15</f>
-        <v>20363212.0</v>
+        <v>19860460.0</v>
       </c>
       <c r="U17">
         <f>T17+U15</f>
-        <v>22030176.0</v>
+        <v>21474071.0</v>
       </c>
       <c r="V17">
         <f>U17+V15</f>
-        <v>23771148.0</v>
+        <v>23159459.0</v>
       </c>
       <c r="W17">
         <f>V17+W15</f>
-        <v>25589509.0</v>
+        <v>24919675.0</v>
       </c>
       <c r="X17">
         <f>W17+X15</f>
-        <v>27488739.0</v>
+        <v>26758157.0</v>
       </c>
       <c r="Y17">
         <f>X17+Y15</f>
-        <v>29472248.0</v>
+        <v>28678270.0</v>
       </c>
       <c r="Z17">
         <f>Y17+Z15</f>
-        <v>31543953.0</v>
+        <v>30683736.0</v>
       </c>
     </row>
   </sheetData>
@@ -2109,79 +2109,79 @@
       </c>
       <c r="H10">
         <f>ROUND(Revenue!H15*Assumptions!$B$11,0)</f>
-        <v>173669.0</v>
+        <v>170832.0</v>
       </c>
       <c r="I10">
         <f>ROUND(Revenue!I15*Assumptions!$B$11,0)</f>
-        <v>181383.0</v>
+        <v>175561.0</v>
       </c>
       <c r="J10">
         <f>ROUND(Revenue!J15*Assumptions!$B$11,0)</f>
-        <v>189413.0</v>
+        <v>183348.0</v>
       </c>
       <c r="K10">
         <f>ROUND(Revenue!K15*Assumptions!$B$11,0)</f>
-        <v>197815.0</v>
+        <v>191503.0</v>
       </c>
       <c r="L10">
         <f>ROUND(Revenue!L15*Assumptions!$B$11,0)</f>
-        <v>206612.0</v>
+        <v>200025.0</v>
       </c>
       <c r="M10">
         <f>ROUND(Revenue!M15*Assumptions!$B$11,0)</f>
-        <v>215799.0</v>
+        <v>208907.0</v>
       </c>
       <c r="N10">
         <f>ROUND(Revenue!N15*Assumptions!$B$11,0)</f>
-        <v>225382.0</v>
+        <v>218182.0</v>
       </c>
       <c r="O10">
         <f>ROUND(Revenue!O15*Assumptions!$B$11,0)</f>
-        <v>235397.0</v>
+        <v>227882.0</v>
       </c>
       <c r="P10">
         <f>ROUND(Revenue!P15*Assumptions!$B$11,0)</f>
-        <v>245845.0</v>
+        <v>238010.0</v>
       </c>
       <c r="Q10">
         <f>ROUND(Revenue!Q15*Assumptions!$B$11,0)</f>
-        <v>256769.0</v>
+        <v>248583.0</v>
       </c>
       <c r="R10">
         <f>ROUND(Revenue!R15*Assumptions!$B$11,0)</f>
-        <v>268179.0</v>
+        <v>259611.0</v>
       </c>
       <c r="S10">
         <f>ROUND(Revenue!S15*Assumptions!$B$11,0)</f>
-        <v>280112.0</v>
+        <v>271155.0</v>
       </c>
       <c r="T10">
         <f>ROUND(Revenue!T15*Assumptions!$B$11,0)</f>
-        <v>292573.0</v>
+        <v>283196.0</v>
       </c>
       <c r="U10">
         <f>ROUND(Revenue!U15*Assumptions!$B$11,0)</f>
-        <v>305555.0</v>
+        <v>295775.0</v>
       </c>
       <c r="V10">
         <f>ROUND(Revenue!V15*Assumptions!$B$11,0)</f>
-        <v>319120.0</v>
+        <v>308932.0</v>
       </c>
       <c r="W10">
         <f>ROUND(Revenue!W15*Assumptions!$B$11,0)</f>
-        <v>333306.0</v>
+        <v>322648.0</v>
       </c>
       <c r="X10">
         <f>ROUND(Revenue!X15*Assumptions!$B$11,0)</f>
-        <v>348129.0</v>
+        <v>336994.0</v>
       </c>
       <c r="Y10">
         <f>ROUND(Revenue!Y15*Assumptions!$B$11,0)</f>
-        <v>363577.0</v>
+        <v>351957.0</v>
       </c>
       <c r="Z10">
         <f>ROUND(Revenue!Z15*Assumptions!$B$11,0)</f>
-        <v>379744.0</v>
+        <v>367602.0</v>
       </c>
     </row>
     <row r="11">
@@ -2212,79 +2212,79 @@
       </c>
       <c r="H11">
         <f>ROUND(Revenue!H15*Assumptions!$B$16,0)</f>
-        <v>120612.0</v>
+        <v>118641.0</v>
       </c>
       <c r="I11">
         <f>ROUND(Revenue!I15*Assumptions!$B$16,0)</f>
-        <v>125968.0</v>
+        <v>121925.0</v>
       </c>
       <c r="J11">
         <f>ROUND(Revenue!J15*Assumptions!$B$16,0)</f>
-        <v>131546.0</v>
+        <v>127334.0</v>
       </c>
       <c r="K11">
         <f>ROUND(Revenue!K15*Assumptions!$B$16,0)</f>
-        <v>137381.0</v>
+        <v>132997.0</v>
       </c>
       <c r="L11">
         <f>ROUND(Revenue!L15*Assumptions!$B$16,0)</f>
-        <v>143490.0</v>
+        <v>138915.0</v>
       </c>
       <c r="M11">
         <f>ROUND(Revenue!M15*Assumptions!$B$16,0)</f>
-        <v>149870.0</v>
+        <v>145084.0</v>
       </c>
       <c r="N11">
         <f>ROUND(Revenue!N15*Assumptions!$B$16,0)</f>
-        <v>156526.0</v>
+        <v>151525.0</v>
       </c>
       <c r="O11">
         <f>ROUND(Revenue!O15*Assumptions!$B$16,0)</f>
-        <v>163481.0</v>
+        <v>158262.0</v>
       </c>
       <c r="P11">
         <f>ROUND(Revenue!P15*Assumptions!$B$16,0)</f>
-        <v>170737.0</v>
+        <v>165295.0</v>
       </c>
       <c r="Q11">
         <f>ROUND(Revenue!Q15*Assumptions!$B$16,0)</f>
-        <v>178324.0</v>
+        <v>172638.0</v>
       </c>
       <c r="R11">
         <f>ROUND(Revenue!R15*Assumptions!$B$16,0)</f>
-        <v>186248.0</v>
+        <v>180297.0</v>
       </c>
       <c r="S11">
         <f>ROUND(Revenue!S15*Assumptions!$B$16,0)</f>
-        <v>194535.0</v>
+        <v>188315.0</v>
       </c>
       <c r="T11">
         <f>ROUND(Revenue!T15*Assumptions!$B$16,0)</f>
-        <v>203189.0</v>
+        <v>196676.0</v>
       </c>
       <c r="U11">
         <f>ROUND(Revenue!U15*Assumptions!$B$16,0)</f>
-        <v>212205.0</v>
+        <v>205413.0</v>
       </c>
       <c r="V11">
         <f>ROUND(Revenue!V15*Assumptions!$B$16,0)</f>
-        <v>221626.0</v>
+        <v>214550.0</v>
       </c>
       <c r="W11">
         <f>ROUND(Revenue!W15*Assumptions!$B$16,0)</f>
-        <v>231477.0</v>
+        <v>224075.0</v>
       </c>
       <c r="X11">
         <f>ROUND(Revenue!X15*Assumptions!$B$16,0)</f>
-        <v>241772.0</v>
+        <v>234039.0</v>
       </c>
       <c r="Y11">
         <f>ROUND(Revenue!Y15*Assumptions!$B$16,0)</f>
-        <v>252501.0</v>
+        <v>244430.0</v>
       </c>
       <c r="Z11">
         <f>ROUND(Revenue!Z15*Assumptions!$B$16,0)</f>
-        <v>263728.0</v>
+        <v>255296.0</v>
       </c>
     </row>
     <row r="12">
@@ -2418,79 +2418,79 @@
       </c>
       <c r="H14">
         <f>H8+H10+H11+H12</f>
-        <v>531253.0</v>
+        <v>526445.0</v>
       </c>
       <c r="I14">
         <f>I8+I10+I11+I12</f>
-        <v>558303.0</v>
+        <v>548438.0</v>
       </c>
       <c r="J14">
         <f>J8+J10+J11+J12</f>
-        <v>585892.0</v>
+        <v>575615.0</v>
       </c>
       <c r="K14">
         <f>K8+K10+K11+K12</f>
-        <v>614110.0</v>
+        <v>603414.0</v>
       </c>
       <c r="L14">
         <f>L8+L10+L11+L12</f>
-        <v>642998.0</v>
+        <v>631836.0</v>
       </c>
       <c r="M14">
         <f>M8+M10+M11+M12</f>
-        <v>672547.0</v>
+        <v>660869.0</v>
       </c>
       <c r="N14">
         <f>N8+N10+N11+N12</f>
-        <v>702768.0</v>
+        <v>690567.0</v>
       </c>
       <c r="O14">
         <f>O8+O10+O11+O12</f>
-        <v>733721.0</v>
+        <v>720987.0</v>
       </c>
       <c r="P14">
         <f>P8+P10+P11+P12</f>
-        <v>765408.0</v>
+        <v>752131.0</v>
       </c>
       <c r="Q14">
         <f>Q8+Q10+Q11+Q12</f>
-        <v>797903.0</v>
+        <v>784031.0</v>
       </c>
       <c r="R14">
         <f>R8+R10+R11+R12</f>
-        <v>831221.0</v>
+        <v>816702.0</v>
       </c>
       <c r="S14">
         <f>S8+S10+S11+S12</f>
-        <v>865426.0</v>
+        <v>850249.0</v>
       </c>
       <c r="T14">
         <f>T8+T10+T11+T12</f>
-        <v>900526.0</v>
+        <v>884636.0</v>
       </c>
       <c r="U14">
         <f>U8+U10+U11+U12</f>
-        <v>936510.0</v>
+        <v>919938.0</v>
       </c>
       <c r="V14">
         <f>V8+V10+V11+V12</f>
-        <v>973482.0</v>
+        <v>956218.0</v>
       </c>
       <c r="W14">
         <f>W8+W10+W11+W12</f>
-        <v>1011506.0</v>
+        <v>993446.0</v>
       </c>
       <c r="X14">
         <f>X8+X10+X11+X12</f>
-        <v>1050611.0</v>
+        <v>1031743.0</v>
       </c>
       <c r="Y14">
         <f>Y8+Y10+Y11+Y12</f>
-        <v>1090775.0</v>
+        <v>1071084.0</v>
       </c>
       <c r="Z14">
         <f>Z8+Z10+Z11+Z12</f>
-        <v>1132157.0</v>
+        <v>1111583.0</v>
       </c>
     </row>
   </sheetData>
@@ -2650,83 +2650,83 @@
       </c>
       <c r="H5">
         <f>Revenue!H15</f>
-        <v>947460.0</v>
+        <v>931981.0</v>
       </c>
       <c r="I5">
         <f>Revenue!I15</f>
-        <v>989540.0</v>
+        <v>957778.0</v>
       </c>
       <c r="J5">
         <f>Revenue!J15</f>
-        <v>1033351.0</v>
+        <v>1000264.0</v>
       </c>
       <c r="K5">
         <f>Revenue!K15</f>
-        <v>1079188.0</v>
+        <v>1044752.0</v>
       </c>
       <c r="L5">
         <f>Revenue!L15</f>
-        <v>1127181.0</v>
+        <v>1091243.0</v>
       </c>
       <c r="M5">
         <f>Revenue!M15</f>
-        <v>1177297.0</v>
+        <v>1139700.0</v>
       </c>
       <c r="N5">
         <f>Revenue!N15</f>
-        <v>1229582.0</v>
+        <v>1190298.0</v>
       </c>
       <c r="O5">
         <f>Revenue!O15</f>
-        <v>1284217.0</v>
+        <v>1243217.0</v>
       </c>
       <c r="P5">
         <f>Revenue!P15</f>
-        <v>1341218.0</v>
+        <v>1298471.0</v>
       </c>
       <c r="Q5">
         <f>Revenue!Q15</f>
-        <v>1400814.0</v>
+        <v>1356154.0</v>
       </c>
       <c r="R5">
         <f>Revenue!R15</f>
-        <v>1463062.0</v>
+        <v>1416319.0</v>
       </c>
       <c r="S5">
         <f>Revenue!S15</f>
-        <v>1528159.0</v>
+        <v>1479298.0</v>
       </c>
       <c r="T5">
         <f>Revenue!T15</f>
-        <v>1596142.0</v>
+        <v>1544984.0</v>
       </c>
       <c r="U5">
         <f>Revenue!U15</f>
-        <v>1666964.0</v>
+        <v>1613611.0</v>
       </c>
       <c r="V5">
         <f>Revenue!V15</f>
-        <v>1740972.0</v>
+        <v>1685388.0</v>
       </c>
       <c r="W5">
         <f>Revenue!W15</f>
-        <v>1818361.0</v>
+        <v>1760216.0</v>
       </c>
       <c r="X5">
         <f>Revenue!X15</f>
-        <v>1899230.0</v>
+        <v>1838482.0</v>
       </c>
       <c r="Y5">
         <f>Revenue!Y15</f>
-        <v>1983509.0</v>
+        <v>1920113.0</v>
       </c>
       <c r="Z5">
         <f>Revenue!Z15</f>
-        <v>2071705.0</v>
+        <v>2005466.0</v>
       </c>
       <c r="AA5">
         <f>SUM(C5:Z5)</f>
-        <v>31543953.0</v>
+        <v>30683736.0</v>
       </c>
     </row>
     <row r="6">
@@ -2757,83 +2757,83 @@
       </c>
       <c r="H6">
         <f>-Costs!H10</f>
-        <v>-173669.0</v>
+        <v>-170832.0</v>
       </c>
       <c r="I6">
         <f>-Costs!I10</f>
-        <v>-181383.0</v>
+        <v>-175561.0</v>
       </c>
       <c r="J6">
         <f>-Costs!J10</f>
-        <v>-189413.0</v>
+        <v>-183348.0</v>
       </c>
       <c r="K6">
         <f>-Costs!K10</f>
-        <v>-197815.0</v>
+        <v>-191503.0</v>
       </c>
       <c r="L6">
         <f>-Costs!L10</f>
-        <v>-206612.0</v>
+        <v>-200025.0</v>
       </c>
       <c r="M6">
         <f>-Costs!M10</f>
-        <v>-215799.0</v>
+        <v>-208907.0</v>
       </c>
       <c r="N6">
         <f>-Costs!N10</f>
-        <v>-225382.0</v>
+        <v>-218182.0</v>
       </c>
       <c r="O6">
         <f>-Costs!O10</f>
-        <v>-235397.0</v>
+        <v>-227882.0</v>
       </c>
       <c r="P6">
         <f>-Costs!P10</f>
-        <v>-245845.0</v>
+        <v>-238010.0</v>
       </c>
       <c r="Q6">
         <f>-Costs!Q10</f>
-        <v>-256769.0</v>
+        <v>-248583.0</v>
       </c>
       <c r="R6">
         <f>-Costs!R10</f>
-        <v>-268179.0</v>
+        <v>-259611.0</v>
       </c>
       <c r="S6">
         <f>-Costs!S10</f>
-        <v>-280112.0</v>
+        <v>-271155.0</v>
       </c>
       <c r="T6">
         <f>-Costs!T10</f>
-        <v>-292573.0</v>
+        <v>-283196.0</v>
       </c>
       <c r="U6">
         <f>-Costs!U10</f>
-        <v>-305555.0</v>
+        <v>-295775.0</v>
       </c>
       <c r="V6">
         <f>-Costs!V10</f>
-        <v>-319120.0</v>
+        <v>-308932.0</v>
       </c>
       <c r="W6">
         <f>-Costs!W10</f>
-        <v>-333306.0</v>
+        <v>-322648.0</v>
       </c>
       <c r="X6">
         <f>-Costs!X10</f>
-        <v>-348129.0</v>
+        <v>-336994.0</v>
       </c>
       <c r="Y6">
         <f>-Costs!Y10</f>
-        <v>-363577.0</v>
+        <v>-351957.0</v>
       </c>
       <c r="Z6">
         <f>-Costs!Z10</f>
-        <v>-379744.0</v>
+        <v>-367602.0</v>
       </c>
       <c r="AA6">
         <f>SUM(C6:Z6)</f>
-        <v>-5782006.0</v>
+        <v>-5624330.0</v>
       </c>
     </row>
     <row r="7">
@@ -2864,83 +2864,83 @@
       </c>
       <c r="H7">
         <f>H5+H6</f>
-        <v>773791.0</v>
+        <v>761149.0</v>
       </c>
       <c r="I7">
         <f>I5+I6</f>
-        <v>808157.0</v>
+        <v>782217.0</v>
       </c>
       <c r="J7">
         <f>J5+J6</f>
-        <v>843938.0</v>
+        <v>816916.0</v>
       </c>
       <c r="K7">
         <f>K5+K6</f>
-        <v>881373.0</v>
+        <v>853249.0</v>
       </c>
       <c r="L7">
         <f>L5+L6</f>
-        <v>920569.0</v>
+        <v>891218.0</v>
       </c>
       <c r="M7">
         <f>M5+M6</f>
-        <v>961498.0</v>
+        <v>930793.0</v>
       </c>
       <c r="N7">
         <f>N5+N6</f>
-        <v>1004200.0</v>
+        <v>972116.0</v>
       </c>
       <c r="O7">
         <f>O5+O6</f>
-        <v>1048820.0</v>
+        <v>1015335.0</v>
       </c>
       <c r="P7">
         <f>P5+P6</f>
-        <v>1095373.0</v>
+        <v>1060461.0</v>
       </c>
       <c r="Q7">
         <f>Q5+Q6</f>
-        <v>1144045.0</v>
+        <v>1107571.0</v>
       </c>
       <c r="R7">
         <f>R5+R6</f>
-        <v>1194883.0</v>
+        <v>1156708.0</v>
       </c>
       <c r="S7">
         <f>S5+S6</f>
-        <v>1248047.0</v>
+        <v>1208143.0</v>
       </c>
       <c r="T7">
         <f>T5+T6</f>
-        <v>1303569.0</v>
+        <v>1261788.0</v>
       </c>
       <c r="U7">
         <f>U5+U6</f>
-        <v>1361409.0</v>
+        <v>1317836.0</v>
       </c>
       <c r="V7">
         <f>V5+V6</f>
-        <v>1421852.0</v>
+        <v>1376456.0</v>
       </c>
       <c r="W7">
         <f>W5+W6</f>
-        <v>1485055.0</v>
+        <v>1437568.0</v>
       </c>
       <c r="X7">
         <f>X5+X6</f>
-        <v>1551101.0</v>
+        <v>1501488.0</v>
       </c>
       <c r="Y7">
         <f>Y5+Y6</f>
-        <v>1619932.0</v>
+        <v>1568156.0</v>
       </c>
       <c r="Z7">
         <f>Z5+Z6</f>
-        <v>1691961.0</v>
+        <v>1637864.0</v>
       </c>
       <c r="AA7">
         <f>SUM(C7:Z7)</f>
-        <v>25761947.0</v>
+        <v>25059406.0</v>
       </c>
     </row>
     <row r="8">
@@ -3181,83 +3181,83 @@
       </c>
       <c r="H11">
         <f>-Costs!H11</f>
-        <v>-120612.0</v>
+        <v>-118641.0</v>
       </c>
       <c r="I11">
         <f>-Costs!I11</f>
-        <v>-125968.0</v>
+        <v>-121925.0</v>
       </c>
       <c r="J11">
         <f>-Costs!J11</f>
-        <v>-131546.0</v>
+        <v>-127334.0</v>
       </c>
       <c r="K11">
         <f>-Costs!K11</f>
-        <v>-137381.0</v>
+        <v>-132997.0</v>
       </c>
       <c r="L11">
         <f>-Costs!L11</f>
-        <v>-143490.0</v>
+        <v>-138915.0</v>
       </c>
       <c r="M11">
         <f>-Costs!M11</f>
-        <v>-149870.0</v>
+        <v>-145084.0</v>
       </c>
       <c r="N11">
         <f>-Costs!N11</f>
-        <v>-156526.0</v>
+        <v>-151525.0</v>
       </c>
       <c r="O11">
         <f>-Costs!O11</f>
-        <v>-163481.0</v>
+        <v>-158262.0</v>
       </c>
       <c r="P11">
         <f>-Costs!P11</f>
-        <v>-170737.0</v>
+        <v>-165295.0</v>
       </c>
       <c r="Q11">
         <f>-Costs!Q11</f>
-        <v>-178324.0</v>
+        <v>-172638.0</v>
       </c>
       <c r="R11">
         <f>-Costs!R11</f>
-        <v>-186248.0</v>
+        <v>-180297.0</v>
       </c>
       <c r="S11">
         <f>-Costs!S11</f>
-        <v>-194535.0</v>
+        <v>-188315.0</v>
       </c>
       <c r="T11">
         <f>-Costs!T11</f>
-        <v>-203189.0</v>
+        <v>-196676.0</v>
       </c>
       <c r="U11">
         <f>-Costs!U11</f>
-        <v>-212205.0</v>
+        <v>-205413.0</v>
       </c>
       <c r="V11">
         <f>-Costs!V11</f>
-        <v>-221626.0</v>
+        <v>-214550.0</v>
       </c>
       <c r="W11">
         <f>-Costs!W11</f>
-        <v>-231477.0</v>
+        <v>-224075.0</v>
       </c>
       <c r="X11">
         <f>-Costs!X11</f>
-        <v>-241772.0</v>
+        <v>-234039.0</v>
       </c>
       <c r="Y11">
         <f>-Costs!Y11</f>
-        <v>-252501.0</v>
+        <v>-244430.0</v>
       </c>
       <c r="Z11">
         <f>-Costs!Z11</f>
-        <v>-263728.0</v>
+        <v>-255296.0</v>
       </c>
       <c r="AA11">
         <f>SUM(C11:Z11)</f>
-        <v>-4015547.0</v>
+        <v>-3906038.0</v>
       </c>
     </row>
     <row r="12">
@@ -3395,83 +3395,83 @@
       </c>
       <c r="H13">
         <f>H10+H11+H12</f>
-        <v>-357584.0</v>
+        <v>-355613.0</v>
       </c>
       <c r="I13">
         <f>I10+I11+I12</f>
-        <v>-376920.0</v>
+        <v>-372877.0</v>
       </c>
       <c r="J13">
         <f>J10+J11+J12</f>
-        <v>-396479.0</v>
+        <v>-392267.0</v>
       </c>
       <c r="K13">
         <f>K10+K11+K12</f>
-        <v>-416295.0</v>
+        <v>-411911.0</v>
       </c>
       <c r="L13">
         <f>L10+L11+L12</f>
-        <v>-436386.0</v>
+        <v>-431811.0</v>
       </c>
       <c r="M13">
         <f>M10+M11+M12</f>
-        <v>-456748.0</v>
+        <v>-451962.0</v>
       </c>
       <c r="N13">
         <f>N10+N11+N12</f>
-        <v>-477386.0</v>
+        <v>-472385.0</v>
       </c>
       <c r="O13">
         <f>O10+O11+O12</f>
-        <v>-498324.0</v>
+        <v>-493105.0</v>
       </c>
       <c r="P13">
         <f>P10+P11+P12</f>
-        <v>-519563.0</v>
+        <v>-514121.0</v>
       </c>
       <c r="Q13">
         <f>Q10+Q11+Q12</f>
-        <v>-541134.0</v>
+        <v>-535448.0</v>
       </c>
       <c r="R13">
         <f>R10+R11+R12</f>
-        <v>-563042.0</v>
+        <v>-557091.0</v>
       </c>
       <c r="S13">
         <f>S10+S11+S12</f>
-        <v>-585314.0</v>
+        <v>-579094.0</v>
       </c>
       <c r="T13">
         <f>T10+T11+T12</f>
-        <v>-607953.0</v>
+        <v>-601440.0</v>
       </c>
       <c r="U13">
         <f>U10+U11+U12</f>
-        <v>-630955.0</v>
+        <v>-624163.0</v>
       </c>
       <c r="V13">
         <f>V10+V11+V12</f>
-        <v>-654362.0</v>
+        <v>-647286.0</v>
       </c>
       <c r="W13">
         <f>W10+W11+W12</f>
-        <v>-678200.0</v>
+        <v>-670798.0</v>
       </c>
       <c r="X13">
         <f>X10+X11+X12</f>
-        <v>-702482.0</v>
+        <v>-694749.0</v>
       </c>
       <c r="Y13">
         <f>Y10+Y11+Y12</f>
-        <v>-727198.0</v>
+        <v>-719127.0</v>
       </c>
       <c r="Z13">
         <f>Z10+Z11+Z12</f>
-        <v>-752413.0</v>
+        <v>-743981.0</v>
       </c>
       <c r="AA13">
         <f>SUM(C13:Z13)</f>
-        <v>-11884242.0</v>
+        <v>-11774733.0</v>
       </c>
     </row>
     <row r="15">
@@ -3502,83 +3502,83 @@
       </c>
       <c r="H15">
         <f>H7+H13</f>
-        <v>416207.0</v>
+        <v>405536.0</v>
       </c>
       <c r="I15">
         <f>I7+I13</f>
-        <v>431237.0</v>
+        <v>409340.0</v>
       </c>
       <c r="J15">
         <f>J7+J13</f>
-        <v>447459.0</v>
+        <v>424649.0</v>
       </c>
       <c r="K15">
         <f>K7+K13</f>
-        <v>465078.0</v>
+        <v>441338.0</v>
       </c>
       <c r="L15">
         <f>L7+L13</f>
-        <v>484183.0</v>
+        <v>459407.0</v>
       </c>
       <c r="M15">
         <f>M7+M13</f>
-        <v>504750.0</v>
+        <v>478831.0</v>
       </c>
       <c r="N15">
         <f>N7+N13</f>
-        <v>526814.0</v>
+        <v>499731.0</v>
       </c>
       <c r="O15">
         <f>O7+O13</f>
-        <v>550496.0</v>
+        <v>522230.0</v>
       </c>
       <c r="P15">
         <f>P7+P13</f>
-        <v>575810.0</v>
+        <v>546340.0</v>
       </c>
       <c r="Q15">
         <f>Q7+Q13</f>
-        <v>602911.0</v>
+        <v>572123.0</v>
       </c>
       <c r="R15">
         <f>R7+R13</f>
-        <v>631841.0</v>
+        <v>599617.0</v>
       </c>
       <c r="S15">
         <f>S7+S13</f>
-        <v>662733.0</v>
+        <v>629049.0</v>
       </c>
       <c r="T15">
         <f>T7+T13</f>
-        <v>695616.0</v>
+        <v>660348.0</v>
       </c>
       <c r="U15">
         <f>U7+U13</f>
-        <v>730454.0</v>
+        <v>693673.0</v>
       </c>
       <c r="V15">
         <f>V7+V13</f>
-        <v>767490.0</v>
+        <v>729170.0</v>
       </c>
       <c r="W15">
         <f>W7+W13</f>
-        <v>806855.0</v>
+        <v>766770.0</v>
       </c>
       <c r="X15">
         <f>X7+X13</f>
-        <v>848619.0</v>
+        <v>806739.0</v>
       </c>
       <c r="Y15">
         <f>Y7+Y13</f>
-        <v>892734.0</v>
+        <v>849029.0</v>
       </c>
       <c r="Z15">
         <f>Z7+Z13</f>
-        <v>939548.0</v>
+        <v>893883.0</v>
       </c>
       <c r="AA15">
         <f>SUM(C15:Z15)</f>
-        <v>13877705.0</v>
+        <v>13284673.0</v>
       </c>
     </row>
     <row r="16">
@@ -3609,79 +3609,79 @@
       </c>
       <c r="H16">
         <f>IF(H5=0,0,ROUND(H15/H5,4))</f>
-        <v>0.4393</v>
+        <v>0.4351</v>
       </c>
       <c r="I16">
         <f>IF(I5=0,0,ROUND(I15/I5,4))</f>
-        <v>0.4358</v>
+        <v>0.4274</v>
       </c>
       <c r="J16">
         <f>IF(J5=0,0,ROUND(J15/J5,4))</f>
-        <v>0.433</v>
+        <v>0.4245</v>
       </c>
       <c r="K16">
         <f>IF(K5=0,0,ROUND(K15/K5,4))</f>
-        <v>0.431</v>
+        <v>0.4224</v>
       </c>
       <c r="L16">
         <f>IF(L5=0,0,ROUND(L15/L5,4))</f>
-        <v>0.4296</v>
+        <v>0.421</v>
       </c>
       <c r="M16">
         <f>IF(M5=0,0,ROUND(M15/M5,4))</f>
-        <v>0.4287</v>
+        <v>0.4201</v>
       </c>
       <c r="N16">
         <f>IF(N5=0,0,ROUND(N15/N5,4))</f>
-        <v>0.4284</v>
+        <v>0.4198</v>
       </c>
       <c r="O16">
         <f>IF(O5=0,0,ROUND(O15/O5,4))</f>
-        <v>0.4287</v>
+        <v>0.4201</v>
       </c>
       <c r="P16">
         <f>IF(P5=0,0,ROUND(P15/P5,4))</f>
-        <v>0.4293</v>
+        <v>0.4208</v>
       </c>
       <c r="Q16">
         <f>IF(Q5=0,0,ROUND(Q15/Q5,4))</f>
-        <v>0.4304</v>
+        <v>0.4219</v>
       </c>
       <c r="R16">
         <f>IF(R5=0,0,ROUND(R15/R5,4))</f>
-        <v>0.4319</v>
+        <v>0.4234</v>
       </c>
       <c r="S16">
         <f>IF(S5=0,0,ROUND(S15/S5,4))</f>
-        <v>0.4337</v>
+        <v>0.4252</v>
       </c>
       <c r="T16">
         <f>IF(T5=0,0,ROUND(T15/T5,4))</f>
-        <v>0.4358</v>
+        <v>0.4274</v>
       </c>
       <c r="U16">
         <f>IF(U5=0,0,ROUND(U15/U5,4))</f>
-        <v>0.4382</v>
+        <v>0.4299</v>
       </c>
       <c r="V16">
         <f>IF(V5=0,0,ROUND(V15/V5,4))</f>
-        <v>0.4408</v>
+        <v>0.4326</v>
       </c>
       <c r="W16">
         <f>IF(W5=0,0,ROUND(W15/W5,4))</f>
-        <v>0.4437</v>
+        <v>0.4356</v>
       </c>
       <c r="X16">
         <f>IF(X5=0,0,ROUND(X15/X5,4))</f>
-        <v>0.4468</v>
+        <v>0.4388</v>
       </c>
       <c r="Y16">
         <f>IF(Y5=0,0,ROUND(Y15/Y5,4))</f>
-        <v>0.4501</v>
+        <v>0.4422</v>
       </c>
       <c r="Z16">
         <f>IF(Z5=0,0,ROUND(Z15/Z5,4))</f>
-        <v>0.4535</v>
+        <v>0.4457</v>
       </c>
     </row>
     <row r="18">
@@ -3712,79 +3712,79 @@
       </c>
       <c r="H18">
         <f>G18+H15</f>
-        <v>2313077.0</v>
+        <v>2302406.0</v>
       </c>
       <c r="I18">
         <f>H18+I15</f>
-        <v>2744314.0</v>
+        <v>2711746.0</v>
       </c>
       <c r="J18">
         <f>I18+J15</f>
-        <v>3191773.0</v>
+        <v>3136395.0</v>
       </c>
       <c r="K18">
         <f>J18+K15</f>
-        <v>3656851.0</v>
+        <v>3577733.0</v>
       </c>
       <c r="L18">
         <f>K18+L15</f>
-        <v>4141034.0</v>
+        <v>4037140.0</v>
       </c>
       <c r="M18">
         <f>L18+M15</f>
-        <v>4645784.0</v>
+        <v>4515971.0</v>
       </c>
       <c r="N18">
         <f>M18+N15</f>
-        <v>5172598.0</v>
+        <v>5015702.0</v>
       </c>
       <c r="O18">
         <f>N18+O15</f>
-        <v>5723094.0</v>
+        <v>5537932.0</v>
       </c>
       <c r="P18">
         <f>O18+P15</f>
-        <v>6298904.0</v>
+        <v>6084272.0</v>
       </c>
       <c r="Q18">
         <f>P18+Q15</f>
-        <v>6901815.0</v>
+        <v>6656395.0</v>
       </c>
       <c r="R18">
         <f>Q18+R15</f>
-        <v>7533656.0</v>
+        <v>7256012.0</v>
       </c>
       <c r="S18">
         <f>R18+S15</f>
-        <v>8196389.0</v>
+        <v>7885061.0</v>
       </c>
       <c r="T18">
         <f>S18+T15</f>
-        <v>8892005.0</v>
+        <v>8545409.0</v>
       </c>
       <c r="U18">
         <f>T18+U15</f>
-        <v>9622459.0</v>
+        <v>9239082.0</v>
       </c>
       <c r="V18">
         <f>U18+V15</f>
-        <v>10389949.0</v>
+        <v>9968252.0</v>
       </c>
       <c r="W18">
         <f>V18+W15</f>
-        <v>11196804.0</v>
+        <v>10735022.0</v>
       </c>
       <c r="X18">
         <f>W18+X15</f>
-        <v>12045423.0</v>
+        <v>11541761.0</v>
       </c>
       <c r="Y18">
         <f>X18+Y15</f>
-        <v>12938157.0</v>
+        <v>12390790.0</v>
       </c>
       <c r="Z18">
         <f>Y18+Z15</f>
-        <v>13877705.0</v>
+        <v>13284673.0</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B3">
         <f>Revenue!Z17</f>
-        <v>31543953.0</v>
+        <v>30683736.0</v>
       </c>
     </row>
     <row r="4">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B4">
         <f>'P&amp;L'!AA15</f>
-        <v>13877705.0</v>
+        <v>13284673.0</v>
       </c>
     </row>
     <row r="5">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B5">
         <f>SUM('P&amp;L'!O15:Z15)</f>
-        <v>8705107.0</v>
+        <v>8268971.0</v>
       </c>
     </row>
     <row r="6">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B7">
         <f>ROUND(B5*B6,0)</f>
-        <v>118389455.0</v>
+        <v>112458006.0</v>
       </c>
     </row>
     <row r="8">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B9">
         <f>B7-B8</f>
-        <v>114839455.0</v>
+        <v>108908006.0</v>
       </c>
     </row>
     <row r="11">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="B11">
         <f>AVERAGE('P&amp;L'!C15:Z15)</f>
-        <v>578237.7083333334</v>
+        <v>553528.0416666666</v>
       </c>
     </row>
     <row r="12">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B12">
         <f>MAX('P&amp;L'!C15:Z15)</f>
-        <v>939548.0</v>
+        <v>893883.0</v>
       </c>
     </row>
     <row r="13">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B14">
         <f>SUMIF('P&amp;L'!C15:Z15,"&gt;0")</f>
-        <v>13877705.0</v>
+        <v>13284673.0</v>
       </c>
     </row>
     <row r="15">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="B15">
         <f>ABS(B12-B13)</f>
-        <v>581061.0</v>
+        <v>535396.0</v>
       </c>
     </row>
   </sheetData>
